--- a/Result/profitability/6218.xlsx
+++ b/Result/profitability/6218.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.07</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.08124999999999999</v>
+        <v>0.27125</v>
       </c>
       <c r="N2" t="n">
-        <v>19.50375</v>
+        <v>21.57625</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -681,7 +681,7 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>1</v>
@@ -690,7 +690,7 @@
         <v>1</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.52</v>
       </c>
       <c r="M3" t="n">
-        <v>0.07750000000000001</v>
+        <v>0.35875</v>
       </c>
       <c r="N3" t="n">
-        <v>25.70125</v>
+        <v>27.26</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.89</v>
       </c>
       <c r="M4" t="n">
-        <v>0.21125</v>
+        <v>0.50125</v>
       </c>
       <c r="N4" t="n">
-        <v>29.33875</v>
+        <v>30.84125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,13 +1018,13 @@
         <v>0.51</v>
       </c>
       <c r="M5" t="n">
-        <v>0.30625</v>
+        <v>0.5862499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>32.255</v>
+        <v>34.27875</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
@@ -1036,7 +1036,7 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0.40375</v>
+        <v>0.695</v>
       </c>
       <c r="N6" t="n">
-        <v>35.7425</v>
+        <v>35.7325</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.23</v>
       </c>
       <c r="M7" t="n">
-        <v>0.465</v>
+        <v>0.78125</v>
       </c>
       <c r="N7" t="n">
-        <v>38.1175</v>
+        <v>41.05374999999999</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1288,7 +1288,7 @@
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,10 +1391,10 @@
         <v>0.14</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5399999999999999</v>
+        <v>0.755</v>
       </c>
       <c r="N8" t="n">
-        <v>41.73</v>
+        <v>42.6125</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>0.445</v>
       </c>
       <c r="N11" t="n">
-        <v>40.81874999999999</v>
+        <v>40.81875</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6218</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>383</v>
+      </c>
+      <c r="D75" t="n">
+        <v>281</v>
+      </c>
+      <c r="E75" t="n">
+        <v>102</v>
+      </c>
+      <c r="F75" t="n">
+        <v>26.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>31</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.04%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>109</v>
+      </c>
+      <c r="J75" t="n">
+        <v>140</v>
+      </c>
+      <c r="K75" t="n">
+        <v>133</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.04374999999999996</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.68375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.914285714285715</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>7.059999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.3603879530372638</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-13.17647058823529</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>16.19</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.547801147227533</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
